--- a/diseases/d195/2026-2029.xlsx
+++ b/diseases/d195/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D195</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Pneumoconiosis</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>尘肺病</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>32</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.4341085271317829</v>
-      </c>
       <c r="O2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.01498389232745415</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -779,7 +953,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -789,27 +963,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -819,22 +993,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d195/2026-2029.xlsx
+++ b/diseases/d195/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>32</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.01498389232745415</v>
       </c>
